--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_36.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_36.xlsx
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ExamGrade</t>
+          <t>Treatment?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.06082075378279985</v>
+        <v>-0.9046313356963417</v>
       </c>
       <c r="C2">
-        <v>-1.519571253098458</v>
+        <v>-0.1840094592713713</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.09341688098535447</v>
+        <v>0.2363661478330751</v>
       </c>
       <c r="C3">
-        <v>0.384677477997118</v>
+        <v>-0.736155743908974</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.03950696910678751</v>
+        <v>-1.147543930423123</v>
       </c>
       <c r="C4">
-        <v>-0.8615146566769659</v>
+        <v>-0.7290989572464688</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.05633088703284</v>
+        <v>-0.7063736304084453</v>
       </c>
       <c r="C5">
-        <v>-0.1588966853130409</v>
+        <v>-1.105253026780489</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.701163545090963</v>
+        <v>0.7761160485535519</v>
       </c>
       <c r="C6">
-        <v>-1.407060512837482</v>
+        <v>-0.04714173898009655</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.193804920302699</v>
+        <v>0.5542980788023624</v>
       </c>
       <c r="C7">
-        <v>-0.7530697988797489</v>
+        <v>-0.1355559530537727</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.9143129631242424</v>
+        <v>0.7951916994959136</v>
       </c>
       <c r="C8">
-        <v>-0.6900270577322136</v>
+        <v>-0.2343804347016338</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.5342812197951907</v>
+        <v>0.5259334473889549</v>
       </c>
       <c r="C9">
-        <v>1.304649330329873</v>
+        <v>-0.247316734438573</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.3271730157101117</v>
+        <v>-0.7010993663730866</v>
       </c>
       <c r="C10">
-        <v>-0.3093215746690501</v>
+        <v>-0.3958721030463565</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-1.353664833854664</v>
+        <v>0.3679484051140146</v>
       </c>
       <c r="C11">
-        <v>0.2151660986783668</v>
+        <v>0.007148842775653447</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-1.232822744761866</v>
+        <v>-0.2111424452563374</v>
       </c>
       <c r="C12">
-        <v>1.939278264544185</v>
+        <v>-1.110674932464291</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.1041563741081114</v>
+        <v>0.7712326142148158</v>
       </c>
       <c r="C13">
-        <v>-0.1780098857080353</v>
+        <v>1.930624100135167</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.4393627811512267</v>
+        <v>-0.1235687425094277</v>
       </c>
       <c r="C14">
-        <v>-0.3461428565694812</v>
+        <v>-0.6643104973354493</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-1.13811880333953</v>
+        <v>1.266829071852681</v>
       </c>
       <c r="C15">
-        <v>1.834630916029018</v>
+        <v>0.1577598965898484</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.4806058720748522</v>
+        <v>-1.262239307391239</v>
       </c>
       <c r="C16">
-        <v>-0.4551074108772571</v>
+        <v>0.6814631379335225</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.0133900243971038</v>
+        <v>-0.01781591868663077</v>
       </c>
       <c r="C17">
-        <v>0.6471892993883553</v>
+        <v>-0.08395861122272059</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-1.148881586298146</v>
+        <v>-0.1839175916701168</v>
       </c>
       <c r="C18">
-        <v>0.0933450651872908</v>
+        <v>-0.03089611793868715</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.7136745206354477</v>
+        <v>1.598050024316942</v>
       </c>
       <c r="C19">
-        <v>-0.8338777941241018</v>
+        <v>-1.667741274347847</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.894511591036477</v>
+        <v>-0.2950320018799072</v>
       </c>
       <c r="C20">
-        <v>0.7478800782222664</v>
+        <v>-1.445067367784954</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-1.042757076017289</v>
+        <v>0.4347277461104791</v>
       </c>
       <c r="C21">
-        <v>-0.783766606493562</v>
+        <v>1.064844897187373</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.02623179149181987</v>
+        <v>0.8629571268405629</v>
       </c>
       <c r="C22">
-        <v>-0.6789027602516119</v>
+        <v>0.4348821317463976</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.2124409626289799</v>
+        <v>0.3626888317712895</v>
       </c>
       <c r="C23">
-        <v>0.2282369363308516</v>
+        <v>0.1254233223850061</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.2380688077771647</v>
+        <v>1.213024060632282</v>
       </c>
       <c r="C24">
-        <v>1.198789082825182</v>
+        <v>2.81811910079353</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.1094505001576119</v>
+        <v>0.1052441766262025</v>
       </c>
       <c r="C25">
-        <v>0.2632292506936628</v>
+        <v>-0.7373742813135695</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.249318957535641</v>
+        <v>0.3575100839231874</v>
       </c>
       <c r="C26">
-        <v>-0.493671082271435</v>
+        <v>-0.8264880796786593</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.7160333880340203</v>
+        <v>0.4839227884221035</v>
       </c>
       <c r="C27">
-        <v>-0.02957809266629929</v>
+        <v>-0.2038406226941267</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.4766750064581371</v>
+        <v>0.1089024218436349</v>
       </c>
       <c r="C28">
-        <v>0.4512386402892925</v>
+        <v>-0.4603892194703527</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.03963168706759514</v>
+        <v>0.6904351164836234</v>
       </c>
       <c r="C29">
-        <v>-0.3862976863976493</v>
+        <v>1.880546441846005</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.5570323449132537</v>
+        <v>0.4007698740090314</v>
       </c>
       <c r="C30">
-        <v>-0.5965524809009035</v>
+        <v>0.8028558109195523</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.06667276963764826</v>
+        <v>0.8014695679882163</v>
       </c>
       <c r="C31">
-        <v>-0.1642628324695765</v>
+        <v>0.9787659709290164</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.9087757308384381</v>
+        <v>2.693961028901617</v>
       </c>
       <c r="C32">
-        <v>0.5352128540137295</v>
+        <v>1.918418077494801</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.578184476679443</v>
+        <v>0.480858854372536</v>
       </c>
       <c r="C33">
-        <v>-0.9968407416879911</v>
+        <v>0.1245099084393657</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.4219324507723555</v>
+        <v>0.5948360253770627</v>
       </c>
       <c r="C34">
-        <v>0.1545508482887011</v>
+        <v>0.9578222942984372</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.1455606485160899</v>
+        <v>0.7855086796106537</v>
       </c>
       <c r="C35">
-        <v>-1.08971004589833</v>
+        <v>1.118047114281798</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.009039297195937166</v>
+        <v>-1.076017825990706</v>
       </c>
       <c r="C36">
-        <v>0.7019549369704468</v>
+        <v>0.2468714645626223</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.3476080840053681</v>
+        <v>0.4926960303606712</v>
       </c>
       <c r="C37">
-        <v>0.3042639725045002</v>
+        <v>-0.4905006666969391</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.246066307708975</v>
+        <v>0.7155526518474077</v>
       </c>
       <c r="C38">
-        <v>-2.098156250582288</v>
+        <v>-0.3474909967680742</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.0740511037444517</v>
+        <v>-0.2511436766052288</v>
       </c>
       <c r="C39">
-        <v>-0.553203006370187</v>
+        <v>-1.372968111824453</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>2.00786129861331</v>
+        <v>2.033613877378959</v>
       </c>
       <c r="C40">
-        <v>-1.276834529585474</v>
+        <v>0.581315514512567</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-1.346135175435268</v>
+        <v>-1.080885392117239</v>
       </c>
       <c r="C41">
-        <v>-0.3434256864709554</v>
+        <v>-0.01691226256883605</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.443838975007044</v>
+        <v>-0.2307553104130574</v>
       </c>
       <c r="C42">
-        <v>0.06073399791835143</v>
+        <v>0.618574898032461</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>1.61329947351992</v>
+        <v>-0.1209365758937585</v>
       </c>
       <c r="C43">
-        <v>-0.8473148176007885</v>
+        <v>-0.7851318337399884</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.1983288904447972</v>
+        <v>-0.3360449592675357</v>
       </c>
       <c r="C44">
-        <v>-0.1328401696026107</v>
+        <v>-1.001947812616147</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.2526852025874112</v>
+        <v>-0.7435555214130355</v>
       </c>
       <c r="C45">
-        <v>-0.04913931550733301</v>
+        <v>0.5770670354933189</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.6267261183446254</v>
+        <v>1.214295436446699</v>
       </c>
       <c r="C46">
-        <v>-0.1400043640550928</v>
+        <v>2.218276442810349</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.1283872499645299</v>
+        <v>0.2789813198584737</v>
       </c>
       <c r="C47">
-        <v>0.05408963848459064</v>
+        <v>-0.5532614594365232</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.7399902144515096</v>
+        <v>0.3062561260781742</v>
       </c>
       <c r="C48">
-        <v>1.032264976231611</v>
+        <v>0.7178347400260463</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.7876587776125207</v>
+        <v>0.4200718308191183</v>
       </c>
       <c r="C49">
-        <v>0.3122448280058816</v>
+        <v>-0.6811156604376839</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.04679126740575381</v>
+        <v>-0.4822550190839064</v>
       </c>
       <c r="C50">
-        <v>0.9415471767677105</v>
+        <v>-0.4935478809067816</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.01632715112130399</v>
+        <v>0.1423801049429133</v>
       </c>
       <c r="C51">
-        <v>-0.8647183419251151</v>
+        <v>0.8093347531366178</v>
       </c>
     </row>
   </sheetData>
